--- a/output/resume_output_cleaned.xlsx
+++ b/output/resume_output_cleaned.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07717c93b0ca7652/Desktop/Personal/coding/resume-extraction/output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_0E958F0D12496E0F62355476585DCE3A8746B354" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE3B0258-BE07-401A-8F05-338EDE589BB9}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_0E958F0D12496E0F62355476585DCE3A8746B354" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDEA0654-8052-4163-B9B0-3A96852A99D7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1258,7 +1258,8 @@
     <col min="4" max="4" width="18.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22.44140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="233.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="255.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="255.6640625" customWidth="1"/>
+    <col min="8" max="8" width="255.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
